--- a/sample_data/erzeugt/Angebot_Muster_Dichtungstechnik.xlsx
+++ b/sample_data/erzeugt/Angebot_Muster_Dichtungstechnik.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15.11.2026</t>
+          <t>16.11.2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
